--- a/00 Raw data/SDG/Summary_SDG.xlsx
+++ b/00 Raw data/SDG/Summary_SDG.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\研究量能追蹤平台\SDG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\線上追蹤平台\研究量能追蹤平台\00 Raw data\SDG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A0BB41-ACCD-4471-BFC5-E2839E61449C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959A4F9A-A064-45D0-8E60-890D2A2A678D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -764,7 +764,7 @@
         <v>661</v>
       </c>
       <c r="O5">
-        <v>825</v>
+        <v>925</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">

--- a/00 Raw data/SDG/Summary_SDG.xlsx
+++ b/00 Raw data/SDG/Summary_SDG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\喬文作業區\線上追蹤平台\研究量能追蹤平台\00 Raw data\SDG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959A4F9A-A064-45D0-8E60-890D2A2A678D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A7F357-D8CC-4EC8-8570-C842D9A3AB21}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -764,7 +764,7 @@
         <v>661</v>
       </c>
       <c r="O5">
-        <v>925</v>
+        <v>825</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">

--- a/00 Raw data/SDG/Summary_SDG.xlsx
+++ b/00 Raw data/SDG/Summary_SDG.xlsx
@@ -57,7 +57,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -504,76 +504,76 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Scholarly Output</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>All publication types</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>393801.0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>38386.0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>37971.0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>39282.0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>42196.0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>46554.0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>48206.0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>45267.0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>46126.0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>49813.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Summary_NFU_SDG | 2017 - 2025</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Field-Weighted Citation Impact</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>included</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>All publication types</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.63</v>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Summary_NKUST_SDG | 2017 - 2025</t>
+          <t>Summary_NFU_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -602,40 +602,40 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.21</v>
+        <v>0.71</v>
       </c>
       <c r="H10" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="I10" t="n">
-        <v>0.86</v>
+        <v>0.76</v>
       </c>
       <c r="J10" t="n">
-        <v>0.89</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>0.59</v>
       </c>
       <c r="M10" t="n">
-        <v>1.47</v>
+        <v>0.97</v>
       </c>
       <c r="N10" t="n">
-        <v>1.45</v>
+        <v>0.51</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>0.77</v>
       </c>
       <c r="P10" t="n">
-        <v>1.01</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Summary_NPUST_SDG | 2017 - 2025</t>
+          <t>Summary_NKUST_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -664,40 +664,40 @@
         </is>
       </c>
       <c r="G11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P11" t="n">
         <v>1.01</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Summary_NTUST_SDG | 2017 - 2025</t>
+          <t>Summary_NPUST_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -726,40 +726,40 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="I12" t="n">
-        <v>1.54</v>
+        <v>0.67</v>
       </c>
       <c r="J12" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="K12" t="n">
-        <v>1.58</v>
+        <v>0.95</v>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>0.98</v>
       </c>
       <c r="M12" t="n">
-        <v>1.45</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>1.51</v>
+        <v>0.99</v>
       </c>
       <c r="O12" t="n">
-        <v>1.37</v>
+        <v>0.96</v>
       </c>
       <c r="P12" t="n">
-        <v>1.51</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Summary_NTUT_SDG | 2017 - 2025</t>
+          <t>Summary_NTUST_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -788,40 +788,40 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="H13" t="n">
-        <v>0.97</v>
+        <v>1.2</v>
       </c>
       <c r="I13" t="n">
-        <v>0.98</v>
+        <v>1.54</v>
       </c>
       <c r="J13" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="K13" t="n">
-        <v>1.17</v>
+        <v>1.58</v>
       </c>
       <c r="L13" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>1.15</v>
+        <v>1.45</v>
       </c>
       <c r="N13" t="n">
-        <v>1.11</v>
+        <v>1.51</v>
       </c>
       <c r="O13" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Summary_YUNTECH_SDG | 2017 - 2025</t>
+          <t>Summary_NTUT_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -850,47 +850,102 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>3.16</v>
+        <v>1.13</v>
       </c>
       <c r="H14" t="n">
-        <v>0.68</v>
+        <v>0.97</v>
       </c>
       <c r="I14" t="n">
-        <v>0.81</v>
+        <v>0.98</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="K14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0</v>
+        <v>1.05</v>
       </c>
       <c r="M14" t="n">
-        <v>3.34</v>
+        <v>1.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2.69</v>
+        <v>1.11</v>
       </c>
       <c r="O14" t="n">
-        <v>7.83</v>
+        <v>1.23</v>
       </c>
       <c r="P14" t="n">
-        <v>3.44</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>Summary_YUNTECH_SDG | 2017 - 2025</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Field-Weighted Citation Impact</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>included</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>All publication types</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Summary_NFU_SDG | 2017 - 2025</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -900,7 +955,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Citations per Publication</t>
+          <t>Field-Weighted Citation Impact</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -919,102 +974,47 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>10.4</v>
+        <v>1.18</v>
       </c>
       <c r="H16" t="n">
-        <v>19.0</v>
+        <v>1.03</v>
       </c>
       <c r="I16" t="n">
-        <v>14.1</v>
+        <v>1.09</v>
       </c>
       <c r="J16" t="n">
-        <v>12.8</v>
+        <v>1.12</v>
       </c>
       <c r="K16" t="n">
-        <v>24.4</v>
+        <v>1.2</v>
       </c>
       <c r="L16" t="n">
-        <v>8.1</v>
+        <v>1.15</v>
       </c>
       <c r="M16" t="n">
-        <v>12.5</v>
+        <v>1.2</v>
       </c>
       <c r="N16" t="n">
-        <v>5.5</v>
+        <v>1.22</v>
       </c>
       <c r="O16" t="n">
-        <v>6.3</v>
+        <v>1.27</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Summary_NKUST_SDG | 2017 - 2025</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Citations per Publication</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>included</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>All publication types</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="I17" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="L17" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="M17" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="P17" t="n">
-        <v>4.1</v>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Summary_NPUST_SDG | 2017 - 2025</t>
+          <t>Summary_NFU_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1043,40 +1043,40 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>14.8</v>
+        <v>10.4</v>
       </c>
       <c r="H18" t="n">
-        <v>31.2</v>
+        <v>19.0</v>
       </c>
       <c r="I18" t="n">
-        <v>22.0</v>
+        <v>14.1</v>
       </c>
       <c r="J18" t="n">
-        <v>24.5</v>
+        <v>12.8</v>
       </c>
       <c r="K18" t="n">
-        <v>22.3</v>
+        <v>24.4</v>
       </c>
       <c r="L18" t="n">
-        <v>19.1</v>
+        <v>8.1</v>
       </c>
       <c r="M18" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="N18" t="n">
-        <v>11.3</v>
+        <v>5.5</v>
       </c>
       <c r="O18" t="n">
-        <v>7.9</v>
+        <v>6.3</v>
       </c>
       <c r="P18" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Summary_NTUST_SDG | 2017 - 2025</t>
+          <t>Summary_NKUST_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1105,40 +1105,40 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>24.8</v>
+        <v>20.1</v>
       </c>
       <c r="H19" t="n">
-        <v>32.2</v>
+        <v>22.6</v>
       </c>
       <c r="I19" t="n">
-        <v>39.6</v>
+        <v>21.6</v>
       </c>
       <c r="J19" t="n">
-        <v>36.0</v>
+        <v>21.2</v>
       </c>
       <c r="K19" t="n">
-        <v>39.9</v>
+        <v>29.9</v>
       </c>
       <c r="L19" t="n">
-        <v>32.8</v>
+        <v>31.6</v>
       </c>
       <c r="M19" t="n">
-        <v>24.8</v>
+        <v>28.5</v>
       </c>
       <c r="N19" t="n">
-        <v>21.7</v>
+        <v>23.2</v>
       </c>
       <c r="O19" t="n">
-        <v>13.7</v>
+        <v>11.4</v>
       </c>
       <c r="P19" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Summary_NTUT_SDG | 2017 - 2025</t>
+          <t>Summary_NPUST_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1167,40 +1167,40 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>18.7</v>
+        <v>14.8</v>
       </c>
       <c r="H20" t="n">
-        <v>28.8</v>
+        <v>31.2</v>
       </c>
       <c r="I20" t="n">
-        <v>26.3</v>
+        <v>22.0</v>
       </c>
       <c r="J20" t="n">
-        <v>26.9</v>
+        <v>24.5</v>
       </c>
       <c r="K20" t="n">
-        <v>28.1</v>
+        <v>22.3</v>
       </c>
       <c r="L20" t="n">
-        <v>21.7</v>
+        <v>19.1</v>
       </c>
       <c r="M20" t="n">
-        <v>20.0</v>
+        <v>15.3</v>
       </c>
       <c r="N20" t="n">
-        <v>14.8</v>
+        <v>11.3</v>
       </c>
       <c r="O20" t="n">
-        <v>11.7</v>
+        <v>7.9</v>
       </c>
       <c r="P20" t="n">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Summary_YUNTECH_SDG | 2017 - 2025</t>
+          <t>Summary_NTUST_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1229,47 +1229,102 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>33.0</v>
+        <v>24.8</v>
       </c>
       <c r="H21" t="n">
-        <v>13.6</v>
+        <v>32.2</v>
       </c>
       <c r="I21" t="n">
-        <v>20.9</v>
+        <v>39.6</v>
       </c>
       <c r="J21" t="n">
-        <v>26.7</v>
+        <v>36.0</v>
       </c>
       <c r="K21" t="n">
-        <v>24.9</v>
+        <v>39.9</v>
       </c>
       <c r="L21" t="n">
-        <v>57.8</v>
+        <v>32.8</v>
       </c>
       <c r="M21" t="n">
-        <v>48.8</v>
+        <v>24.8</v>
       </c>
       <c r="N21" t="n">
-        <v>29.7</v>
+        <v>21.7</v>
       </c>
       <c r="O21" t="n">
-        <v>48.0</v>
+        <v>13.7</v>
       </c>
       <c r="P21" t="n">
-        <v>10.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>Summary_NTUT_SDG | 2017 - 2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Citations per Publication</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>included</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>All publication types</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="P22" t="n">
+        <v>5.4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Summary_NFU_SDG | 2017 - 2025</t>
+          <t>Summary_YUNTECH_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1279,7 +1334,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Output in Top 10% Citation Percentiles (%)</t>
+          <t>Citations per Publication</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1294,44 +1349,44 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>in top 10% of the world</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>6.6</v>
+        <v>33.0</v>
       </c>
       <c r="H23" t="n">
-        <v>13.0</v>
+        <v>13.6</v>
       </c>
       <c r="I23" t="n">
-        <v>7.4</v>
+        <v>20.9</v>
       </c>
       <c r="J23" t="n">
-        <v>5.0</v>
+        <v>26.7</v>
       </c>
       <c r="K23" t="n">
-        <v>6.5</v>
+        <v>24.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3</v>
+        <v>57.8</v>
       </c>
       <c r="M23" t="n">
-        <v>6.2</v>
+        <v>48.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2.9</v>
+        <v>29.7</v>
       </c>
       <c r="O23" t="n">
-        <v>7.3</v>
+        <v>48.0</v>
       </c>
       <c r="P23" t="n">
-        <v>9.2</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Summary_NKUST_SDG | 2017 - 2025</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1341,7 +1396,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Output in Top 10% Citation Percentiles (%)</t>
+          <t>Citations per Publication</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1356,106 +1411,51 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>in top 10% of the world</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>21.2</v>
+        <v>17.8</v>
       </c>
       <c r="H24" t="n">
-        <v>11.6</v>
+        <v>25.5</v>
       </c>
       <c r="I24" t="n">
-        <v>12.4</v>
+        <v>25.5</v>
       </c>
       <c r="J24" t="n">
-        <v>11.2</v>
+        <v>24.9</v>
       </c>
       <c r="K24" t="n">
-        <v>20.1</v>
+        <v>26.5</v>
       </c>
       <c r="L24" t="n">
-        <v>23.6</v>
+        <v>21.1</v>
       </c>
       <c r="M24" t="n">
-        <v>26.9</v>
+        <v>16.9</v>
       </c>
       <c r="N24" t="n">
-        <v>29.1</v>
+        <v>13.0</v>
       </c>
       <c r="O24" t="n">
-        <v>20.2</v>
+        <v>8.9</v>
       </c>
       <c r="P24" t="n">
-        <v>20.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Summary_NPUST_SDG | 2017 - 2025</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Output in Top 10% Citation Percentiles (%)</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>included</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>All publication types</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>in top 10% of the world</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="H25" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="K25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="L25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N25" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="O25" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="P25" t="n">
-        <v>14.9</v>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Summary_NTUST_SDG | 2017 - 2025</t>
+          <t>Summary_NFU_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1484,40 +1484,40 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>26.5</v>
+        <v>6.6</v>
       </c>
       <c r="H26" t="n">
-        <v>16.5</v>
+        <v>13.0</v>
       </c>
       <c r="I26" t="n">
-        <v>21.7</v>
+        <v>7.4</v>
       </c>
       <c r="J26" t="n">
-        <v>23.3</v>
+        <v>5.0</v>
       </c>
       <c r="K26" t="n">
-        <v>26.0</v>
+        <v>6.5</v>
       </c>
       <c r="L26" t="n">
-        <v>27.9</v>
+        <v>1.3</v>
       </c>
       <c r="M26" t="n">
-        <v>26.2</v>
+        <v>6.2</v>
       </c>
       <c r="N26" t="n">
-        <v>32.0</v>
+        <v>2.9</v>
       </c>
       <c r="O26" t="n">
-        <v>30.3</v>
+        <v>7.3</v>
       </c>
       <c r="P26" t="n">
-        <v>26.8</v>
+        <v>9.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Summary_NTUT_SDG | 2017 - 2025</t>
+          <t>Summary_NKUST_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1546,40 +1546,40 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>20.0</v>
+        <v>21.2</v>
       </c>
       <c r="H27" t="n">
-        <v>16.2</v>
+        <v>11.6</v>
       </c>
       <c r="I27" t="n">
-        <v>14.3</v>
+        <v>12.4</v>
       </c>
       <c r="J27" t="n">
-        <v>15.6</v>
+        <v>11.2</v>
       </c>
       <c r="K27" t="n">
-        <v>17.3</v>
+        <v>20.1</v>
       </c>
       <c r="L27" t="n">
-        <v>18.2</v>
+        <v>23.6</v>
       </c>
       <c r="M27" t="n">
-        <v>19.6</v>
+        <v>26.9</v>
       </c>
       <c r="N27" t="n">
-        <v>20.9</v>
+        <v>29.1</v>
       </c>
       <c r="O27" t="n">
-        <v>23.3</v>
+        <v>20.2</v>
       </c>
       <c r="P27" t="n">
-        <v>26.7</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Summary_YUNTECH_SDG | 2017 - 2025</t>
+          <t>Summary_NPUST_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1608,47 +1608,102 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>25.3</v>
+        <v>13.3</v>
       </c>
       <c r="H28" t="n">
-        <v>5.8</v>
+        <v>17.8</v>
       </c>
       <c r="I28" t="n">
-        <v>10.9</v>
+        <v>8.6</v>
       </c>
       <c r="J28" t="n">
-        <v>14.7</v>
+        <v>13.6</v>
       </c>
       <c r="K28" t="n">
-        <v>16.0</v>
+        <v>11.1</v>
       </c>
       <c r="L28" t="n">
-        <v>23.9</v>
+        <v>17.5</v>
       </c>
       <c r="M28" t="n">
-        <v>31.7</v>
+        <v>12.6</v>
       </c>
       <c r="N28" t="n">
-        <v>30.7</v>
+        <v>11.3</v>
       </c>
       <c r="O28" t="n">
-        <v>33.5</v>
+        <v>11.6</v>
       </c>
       <c r="P28" t="n">
-        <v>30.8</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>Summary_NTUST_SDG | 2017 - 2025</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Output in Top 10% Citation Percentiles (%)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>included</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>All publication types</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>in top 10% of the world</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="M29" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="N29" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="P29" t="n">
+        <v>26.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Summary_NFU_SDG | 2017 - 2025</t>
+          <t>Summary_NTUT_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1658,12 +1713,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Publications in Top 10% Journal Percentiles by CiteScore Percentile (%)</t>
+          <t>Output in Top 10% Citation Percentiles (%)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>included</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1673,44 +1728,44 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>in top 10% by CiteScore Percentile</t>
+          <t>in top 10% of the world</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>19.9</v>
+        <v>20.0</v>
       </c>
       <c r="H30" t="n">
-        <v>25.0</v>
+        <v>16.2</v>
       </c>
       <c r="I30" t="n">
-        <v>12.5</v>
+        <v>14.3</v>
       </c>
       <c r="J30" t="n">
-        <v>21.6</v>
+        <v>15.6</v>
       </c>
       <c r="K30" t="n">
-        <v>20.0</v>
+        <v>17.3</v>
       </c>
       <c r="L30" t="n">
-        <v>17.6</v>
+        <v>18.2</v>
       </c>
       <c r="M30" t="n">
-        <v>20.0</v>
+        <v>19.6</v>
       </c>
       <c r="N30" t="n">
-        <v>12.8</v>
+        <v>20.9</v>
       </c>
       <c r="O30" t="n">
-        <v>25.3</v>
+        <v>23.3</v>
       </c>
       <c r="P30" t="n">
-        <v>21.9</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Summary_NKUST_SDG | 2017 - 2025</t>
+          <t>Summary_YUNTECH_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1720,12 +1775,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Publications in Top 10% Journal Percentiles by CiteScore Percentile (%)</t>
+          <t>Output in Top 10% Citation Percentiles (%)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>included</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1735,44 +1790,44 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>in top 10% by CiteScore Percentile</t>
+          <t>in top 10% of the world</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>37.9</v>
+        <v>25.3</v>
       </c>
       <c r="H31" t="n">
-        <v>30.0</v>
+        <v>5.8</v>
       </c>
       <c r="I31" t="n">
-        <v>20.7</v>
+        <v>10.9</v>
       </c>
       <c r="J31" t="n">
-        <v>34.4</v>
+        <v>14.7</v>
       </c>
       <c r="K31" t="n">
-        <v>28.0</v>
+        <v>16.0</v>
       </c>
       <c r="L31" t="n">
-        <v>35.3</v>
+        <v>23.9</v>
       </c>
       <c r="M31" t="n">
-        <v>33.1</v>
+        <v>31.7</v>
       </c>
       <c r="N31" t="n">
-        <v>41.8</v>
+        <v>30.7</v>
       </c>
       <c r="O31" t="n">
-        <v>48.6</v>
+        <v>33.5</v>
       </c>
       <c r="P31" t="n">
-        <v>45.3</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Summary_NPUST_SDG | 2017 - 2025</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1782,12 +1837,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Publications in Top 10% Journal Percentiles by CiteScore Percentile (%)</t>
+          <t>Output in Top 10% Citation Percentiles (%)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>included</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1797,106 +1852,51 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>in top 10% by CiteScore Percentile</t>
+          <t>in top 10% of the world</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>27.5</v>
+        <v>12.7</v>
       </c>
       <c r="H32" t="n">
-        <v>30.1</v>
+        <v>10.4</v>
       </c>
       <c r="I32" t="n">
-        <v>18.7</v>
+        <v>11.5</v>
       </c>
       <c r="J32" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="O32" t="n">
         <v>13.4</v>
       </c>
-      <c r="K32" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="L32" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="M32" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>39.4</v>
-      </c>
       <c r="P32" t="n">
-        <v>34.2</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Summary_NTUST_SDG | 2017 - 2025</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Publications in Top 10% Journal Percentiles by CiteScore Percentile (%)</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>All publication types</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>in top 10% by CiteScore Percentile</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="H33" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="I33" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="J33" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="K33" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="L33" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="M33" t="n">
-        <v>45.3</v>
-      </c>
-      <c r="N33" t="n">
-        <v>51.9</v>
-      </c>
-      <c r="O33" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="P33" t="n">
-        <v>51.2</v>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Summary_NTUT_SDG | 2017 - 2025</t>
+          <t>Summary_NFU_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1925,40 +1925,40 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>38.8</v>
+        <v>19.9</v>
       </c>
       <c r="H34" t="n">
-        <v>39.8</v>
+        <v>25.0</v>
       </c>
       <c r="I34" t="n">
-        <v>32.0</v>
+        <v>12.5</v>
       </c>
       <c r="J34" t="n">
-        <v>35.5</v>
+        <v>21.6</v>
       </c>
       <c r="K34" t="n">
-        <v>39.6</v>
+        <v>20.0</v>
       </c>
       <c r="L34" t="n">
-        <v>32.8</v>
+        <v>17.6</v>
       </c>
       <c r="M34" t="n">
-        <v>35.8</v>
+        <v>20.0</v>
       </c>
       <c r="N34" t="n">
-        <v>35.4</v>
+        <v>12.8</v>
       </c>
       <c r="O34" t="n">
-        <v>42.9</v>
+        <v>25.3</v>
       </c>
       <c r="P34" t="n">
-        <v>47.9</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Summary_YUNTECH_SDG | 2017 - 2025</t>
+          <t>Summary_NKUST_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1990,44 +1990,99 @@
         <v>37.9</v>
       </c>
       <c r="H35" t="n">
-        <v>24.2</v>
+        <v>30.0</v>
       </c>
       <c r="I35" t="n">
-        <v>29.5</v>
+        <v>20.7</v>
       </c>
       <c r="J35" t="n">
-        <v>25.2</v>
+        <v>34.4</v>
       </c>
       <c r="K35" t="n">
-        <v>24.6</v>
+        <v>28.0</v>
       </c>
       <c r="L35" t="n">
-        <v>35.0</v>
+        <v>35.3</v>
       </c>
       <c r="M35" t="n">
-        <v>41.4</v>
+        <v>33.1</v>
       </c>
       <c r="N35" t="n">
-        <v>40.6</v>
+        <v>41.8</v>
       </c>
       <c r="O35" t="n">
-        <v>46.9</v>
+        <v>48.6</v>
       </c>
       <c r="P35" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>Summary_NPUST_SDG | 2017 - 2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Publications in Top 10% Journal Percentiles by CiteScore Percentile (%)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>All publication types</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>in top 10% by CiteScore Percentile</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H36" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="M36" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="N36" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>34.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Summary_NFU_SDG | 2017 - 2025</t>
+          <t>Summary_NTUST_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2037,7 +2092,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>International Collaboration (%)</t>
+          <t>Publications in Top 10% Journal Percentiles by CiteScore Percentile (%)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2052,44 +2107,44 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>in top 10% by CiteScore Percentile</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>17.9</v>
+        <v>48.8</v>
       </c>
       <c r="H37" t="n">
-        <v>15.9</v>
+        <v>48.7</v>
       </c>
       <c r="I37" t="n">
-        <v>10.3</v>
+        <v>49.5</v>
       </c>
       <c r="J37" t="n">
-        <v>11.7</v>
+        <v>45.3</v>
       </c>
       <c r="K37" t="n">
-        <v>19.4</v>
+        <v>43.4</v>
       </c>
       <c r="L37" t="n">
-        <v>24.0</v>
+        <v>45.8</v>
       </c>
       <c r="M37" t="n">
-        <v>24.7</v>
+        <v>45.3</v>
       </c>
       <c r="N37" t="n">
-        <v>7.8</v>
+        <v>51.9</v>
       </c>
       <c r="O37" t="n">
-        <v>19.8</v>
+        <v>54.5</v>
       </c>
       <c r="P37" t="n">
-        <v>24.4</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Summary_NKUST_SDG | 2017 - 2025</t>
+          <t>Summary_NTUT_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2099,7 +2154,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>International Collaboration (%)</t>
+          <t>Publications in Top 10% Journal Percentiles by CiteScore Percentile (%)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2114,44 +2169,44 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>in top 10% by CiteScore Percentile</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>41.6</v>
+        <v>38.8</v>
       </c>
       <c r="H38" t="n">
-        <v>19.8</v>
+        <v>39.8</v>
       </c>
       <c r="I38" t="n">
-        <v>32.4</v>
+        <v>32.0</v>
       </c>
       <c r="J38" t="n">
-        <v>25.0</v>
+        <v>35.5</v>
       </c>
       <c r="K38" t="n">
-        <v>41.0</v>
+        <v>39.6</v>
       </c>
       <c r="L38" t="n">
-        <v>41.7</v>
+        <v>32.8</v>
       </c>
       <c r="M38" t="n">
-        <v>45.5</v>
+        <v>35.8</v>
       </c>
       <c r="N38" t="n">
-        <v>48.5</v>
+        <v>35.4</v>
       </c>
       <c r="O38" t="n">
-        <v>44.3</v>
+        <v>42.9</v>
       </c>
       <c r="P38" t="n">
-        <v>48.7</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Summary_NPUST_SDG | 2017 - 2025</t>
+          <t>Summary_YUNTECH_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2161,7 +2216,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>International Collaboration (%)</t>
+          <t>Publications in Top 10% Journal Percentiles by CiteScore Percentile (%)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2176,44 +2231,44 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>in top 10% by CiteScore Percentile</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>37.9</v>
       </c>
       <c r="H39" t="n">
-        <v>23.8</v>
+        <v>24.2</v>
       </c>
       <c r="I39" t="n">
-        <v>32.1</v>
+        <v>29.5</v>
       </c>
       <c r="J39" t="n">
-        <v>31.8</v>
+        <v>25.2</v>
       </c>
       <c r="K39" t="n">
-        <v>34.0</v>
+        <v>24.6</v>
       </c>
       <c r="L39" t="n">
-        <v>38.7</v>
+        <v>35.0</v>
       </c>
       <c r="M39" t="n">
-        <v>40.3</v>
+        <v>41.4</v>
       </c>
       <c r="N39" t="n">
-        <v>36.7</v>
+        <v>40.6</v>
       </c>
       <c r="O39" t="n">
-        <v>40.9</v>
+        <v>46.9</v>
       </c>
       <c r="P39" t="n">
-        <v>45.7</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Summary_NTUST_SDG | 2017 - 2025</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2223,7 +2278,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>International Collaboration (%)</t>
+          <t>Publications in Top 10% Journal Percentiles by CiteScore Percentile (%)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2238,106 +2293,51 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>in top 10% by CiteScore Percentile</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>42.9</v>
+        <v>31.5</v>
       </c>
       <c r="H40" t="n">
-        <v>33.1</v>
+        <v>33.9</v>
       </c>
       <c r="I40" t="n">
-        <v>35.0</v>
+        <v>30.6</v>
       </c>
       <c r="J40" t="n">
-        <v>35.9</v>
+        <v>29.1</v>
       </c>
       <c r="K40" t="n">
-        <v>42.7</v>
+        <v>30.2</v>
       </c>
       <c r="L40" t="n">
-        <v>46.2</v>
+        <v>30.8</v>
       </c>
       <c r="M40" t="n">
-        <v>40.9</v>
+        <v>28.5</v>
       </c>
       <c r="N40" t="n">
-        <v>45.5</v>
+        <v>33.0</v>
       </c>
       <c r="O40" t="n">
-        <v>48.2</v>
+        <v>33.3</v>
       </c>
       <c r="P40" t="n">
-        <v>47.0</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Summary_NTUT_SDG | 2017 - 2025</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>International Collaboration (%)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>All publication types</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="H41" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="I41" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="J41" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="K41" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="L41" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="M41" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="O41" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="P41" t="n">
-        <v>49.9</v>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Summary_YUNTECH_SDG | 2017 - 2025</t>
+          <t>Summary_NFU_SDG | 2017 - 2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2366,59 +2366,431 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>48.7</v>
+        <v>17.9</v>
       </c>
       <c r="H42" t="n">
-        <v>14.6</v>
+        <v>15.9</v>
       </c>
       <c r="I42" t="n">
-        <v>21.8</v>
+        <v>10.3</v>
       </c>
       <c r="J42" t="n">
-        <v>27.6</v>
+        <v>11.7</v>
       </c>
       <c r="K42" t="n">
-        <v>37.8</v>
+        <v>19.4</v>
       </c>
       <c r="L42" t="n">
-        <v>50.7</v>
+        <v>24.0</v>
       </c>
       <c r="M42" t="n">
-        <v>63.1</v>
+        <v>24.7</v>
       </c>
       <c r="N42" t="n">
-        <v>55.8</v>
+        <v>7.8</v>
       </c>
       <c r="O42" t="n">
-        <v>56.4</v>
+        <v>19.8</v>
       </c>
       <c r="P42" t="n">
-        <v>58.4</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>Summary_NKUST_SDG | 2017 - 2025</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>International Collaboration (%)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>All publication types</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="H43" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="I43" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="J43" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="M43" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="N43" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="O43" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>48.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>Summary_NPUST_SDG | 2017 - 2025</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>International Collaboration (%)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>All publication types</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="H44" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I44" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="K44" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="M44" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="N44" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="O44" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="P44" t="n">
+        <v>45.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t/>
-        </is>
+          <t>Summary_NTUST_SDG | 2017 - 2025</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>International Collaboration (%)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>All publication types</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="H45" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="K45" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="L45" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="N45" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="O45" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="P45" t="n">
+        <v>47.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
+        <is>
+          <t>Summary_NTUT_SDG | 2017 - 2025</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>International Collaboration (%)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>All publication types</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="I46" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="K46" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="L46" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="M46" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="O46" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="P46" t="n">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Summary_YUNTECH_SDG | 2017 - 2025</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>International Collaboration (%)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>All publication types</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="H47" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="I47" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J47" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="K47" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="L47" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="M47" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="O47" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="P47" t="n">
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>International Collaboration (%)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>All publication types</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="J48" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L48" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="P48" t="n">
+        <v>43.9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>© 2026 Elsevier B.V. All rights reserved. SciVal, RELX Group and the RE symbol are trade marks of RELX Intellectual Properties SA, used under license.</t>
         </is>
@@ -2454,7 +2826,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Summary_NFU_SDG | 2017 - 2025, Summary_NKUST_SDG | 2017 - 2025, Summary_NPUST_SDG | 2017 - 2025, Summary_NTUST_SDG | 2017 - 2025, Summary_NTUT_SDG | 2017 - 2025, Summary_YUNTECH_SDG | 2017 - 2025</t>
+          <t>Summary_NFU_SDG | 2017 - 2025, Summary_NKUST_SDG | 2017 - 2025, Summary_NPUST_SDG | 2017 - 2025, Summary_NTUST_SDG | 2017 - 2025, Summary_NTUT_SDG | 2017 - 2025, Summary_YUNTECH_SDG | 2017 - 2025, Taiwan</t>
         </is>
       </c>
     </row>
